--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1632.06</v>
+        <v>1622.28</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7174.39</v>
+        <v>7201.57</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>66743.77</v>
+        <v>66575.25999999999</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>623.86</v>
+        <v>621.12</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10382.81</v>
+        <v>10269.86</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1374.83</v>
+        <v>1379.08</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>911.24</v>
+        <v>908.83</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>221389.72</v>
+        <v>216839.78</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2142.93</v>
+        <v>2163.28</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>20782.62</v>
+        <v>20863.75</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>857.17</v>
+        <v>861.54</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3510.32</v>
+        <v>3517.8</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>526.33</v>
+        <v>517.84</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1826.05</v>
+        <v>1817.07</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,68 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>212.68</v>
+        <v>211.64</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1495208-17-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>11707.46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES REGION DE NUBLE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4886-60-CM26</t>
+          <t>2467-824-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>861.54</v>
+        <v>3517.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2467-824-CM26</t>
+          <t>2467-871-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3517.8</v>
+        <v>517.84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2467-871-CM26</t>
+          <t>2467-894-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>517.84</v>
+        <v>1817.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2467-894-CM26</t>
+          <t>1495208-17-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1817.07</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4886-97-CM26</t>
+          <t>2467-1158-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>INVERSIONES LOF SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>77.498.695-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>211.64</v>
+        <v>6450.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1495208-17-CM26</t>
+          <t>1059109-94-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,129 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11707.46</v>
+        <v>30258.13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2467-1224-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Julio Saavedra</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.248.427-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>1625.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1059109-101-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>926.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
@@ -1355,7 +1355,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1420,11 @@
           <t>77.498.695-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1615,6 +1615,311 @@
       </c>
       <c r="M19" s="2" t="n">
         <v>926.26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2467-1285-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.604.912-5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>1637.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2467-1308-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Julio Saavedra</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.248.427-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>244.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2467-1242-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.604.912-5</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>29584.05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1059109-109-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Julio Saavedra</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.248.427-7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>44861.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2467-1321-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.604.912-5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>295.68</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/nuble.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
